--- a/DATASET_SMA PALU.xlsx
+++ b/DATASET_SMA PALU.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/feffee59f62ed9de/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/FEFFEE59F62ED9DE/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8D9E80F-3BE2-4EC9-8CE1-7F5F1583C0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{B8D9E80F-3BE2-4EC9-8CE1-7F5F1583C0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE69E003-51C7-48FD-8E63-94AED91D2DDC}"/>
   <bookViews>
-    <workbookView xWindow="2856" yWindow="2856" windowWidth="17280" windowHeight="9960" xr2:uid="{B5954745-9F08-4A48-84A5-AFC58B71E24A}"/>
+    <workbookView xWindow="2508" yWindow="2508" windowWidth="17280" windowHeight="9960" xr2:uid="{B5954745-9F08-4A48-84A5-AFC58B71E24A}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset Kecil" sheetId="1" r:id="rId1"/>
@@ -68,15 +68,6 @@
     <t>Negeri</t>
   </si>
   <si>
-    <t>J.MURID (Y)</t>
-  </si>
-  <si>
-    <t>J. GURU (X2)</t>
-  </si>
-  <si>
-    <t>J. SEKOLAH (X1)</t>
-  </si>
-  <si>
     <t>STATUS SEKOLAH</t>
   </si>
   <si>
@@ -84,6 +75,15 @@
   </si>
   <si>
     <t>TAHUN</t>
+  </si>
+  <si>
+    <t>Jumlah Guru (X2)</t>
+  </si>
+  <si>
+    <t>Jumlah Siswa (Y)</t>
+  </si>
+  <si>
+    <t>Jumlah Sekolah (X1)</t>
   </si>
 </sst>
 </file>
@@ -204,6 +204,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F48298A5-D0AB-40A3-BAF0-5516A5542E62}" name="Table13" displayName="Table13" ref="A1:F113" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:F113" xr:uid="{3BE93F1C-1ACA-4526-A2B9-A70ABE5C8A4F}"/>
@@ -214,9 +218,9 @@
     <tableColumn id="1" xr3:uid="{4E765A88-EF83-43C1-BEC7-60A9634BE046}" name="TAHUN"/>
     <tableColumn id="2" xr3:uid="{D8CC74A6-0D00-410F-8407-DD85E7E15B81}" name="KECAMATAN" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{0C6A022D-281A-46BB-AE55-90F6FBD1D20E}" name="STATUS SEKOLAH" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{135E1DAE-ACB9-460C-8303-B416E818656F}" name="J. SEKOLAH (X1)"/>
-    <tableColumn id="5" xr3:uid="{83E32369-03F4-4C23-88F6-8C6E24D46214}" name="J. GURU (X2)"/>
-    <tableColumn id="6" xr3:uid="{0A5404FD-CA0F-45E3-BDA2-86207BE809F8}" name="J.MURID (Y)"/>
+    <tableColumn id="4" xr3:uid="{135E1DAE-ACB9-460C-8303-B416E818656F}" name="Jumlah Sekolah (X1)"/>
+    <tableColumn id="5" xr3:uid="{83E32369-03F4-4C23-88F6-8C6E24D46214}" name="Jumlah Guru (X2)"/>
+    <tableColumn id="6" xr3:uid="{0A5404FD-CA0F-45E3-BDA2-86207BE809F8}" name="Jumlah Siswa (Y)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -530,22 +534,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
